--- a/evaluation_forms/042_sustainable_health_care_design_project_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/042_sustainable_health_care_design_project_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sustainability_features</t>
+          <t>Sustainability Features</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>stakeholder_engagement</t>
+          <t>Stakeholder Engagement</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>site_characteristics</t>
+          <t>Site Characteristics</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>project_team</t>
+          <t>Project Team</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>Project Status</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>overall_performance</t>
+          <t>Overall Performance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>project_location</t>
+          <t>Project Location</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,10 +709,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>project_size</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Project Size</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter a numerical value</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -732,10 +736,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>project_budget</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Project Budget</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter a numerical value</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -755,7 +763,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>project_start_date</t>
+          <t>Project Start Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,310 +786,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>project_end_date</t>
+          <t>Project End Date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>project_completion_date</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>project_completion_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>project_value</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>project_value</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>project_cost</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>project_cost</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>project_status_change_date</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>project_status_change_date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>project_status_change_reason</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>project_status_change_reason</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>overall_satisfaction</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>overall_satisfaction</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>user_rating</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>user_rating</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>user_review</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>user_review</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>sustainability_features</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>sustainability_features</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>site_characteristics</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>site_characteristics</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>project_team</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>project_team</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>overall_performance</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>overall_performance</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>user_rating</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>user_rating</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1579,465 +1288,6 @@
       <c r="C28" t="inlineStr">
         <is>
           <t>Suburban</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>user_rating_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>user_rating_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>user_rating_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>sustainability_features_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>commissioning_and_building_performance</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Commissioning and Building Performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>sustainability_features_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>green_building_and_energy_efficiency</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Green Building and Energy Efficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>sustainability_features_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>material_selection_and_waste_management</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Material Selection and Waste Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>sustainability_features_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>sustainable_materials_and_products</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Sustainable Materials and Products</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sustainability_features_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>water_conservation</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Water Conservation</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>site_characteristics_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>building_type_-_hospital</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Building Type - Hospital</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>site_characteristics_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>building_type_-_healthcare_office</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Building Type - Healthcare Office</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>site_characteristics_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>number_of_floors_-_1-2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Number of Floors - 1-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>site_characteristics_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>number_of_floors_-_3-5</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Number of Floors - 3-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>site_characteristics_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>number_of_floors_-_6_or_more</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Number of Floors - 6 or more</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>project_team_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>architect/designer</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Architect/Designer</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>project_team_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>engineer</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>project_team_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>contractor</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>project_team_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>project_team_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>facility_manager</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Facility Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>overall_performance_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>overall_performance_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>overall_performance_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>user_rating_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>user_rating_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>user_rating_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Low</t>
         </is>
       </c>
     </row>
